--- a/6 XUAN 2.xlsx
+++ b/6 XUAN 2.xlsx
@@ -1,113 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\69450\projects\3000\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B058B07C-136D-4020-9A6A-A24B450B32C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="10508" windowHeight="5502"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
-  <si>
-    <t>谴责；指责</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="261">
+  <si>
+    <t>谴责；指责，批评</t>
   </si>
   <si>
     <t>reprehended</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>decried</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>deride</t>
   </si>
   <si>
-    <t>deride</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>castigation</t>
+  </si>
+  <si>
+    <t>censure（反对）</t>
+  </si>
+  <si>
+    <t>fulminate（大声斥责）</t>
   </si>
   <si>
     <t>嘲笑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boo</t>
+  </si>
+  <si>
+    <t>结合，混合</t>
   </si>
   <si>
     <t>hybridity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>eclecticism</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结合，混合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>辨认出，找到</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>discerned by</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>discovered by</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显眼的</t>
   </si>
   <si>
     <t>conspicuous</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>显眼的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>prominent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>超过，胜过</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>outstripped</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>surpassed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>静止的</t>
   </si>
   <si>
     <t>quiescent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>invariant</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>静止的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>古老的，过时的</t>
   </si>
   <si>
     <t>archaic</t>
@@ -116,162 +110,127 @@
     <t>fusty </t>
   </si>
   <si>
-    <t>古老的，过时的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>麻木不仁的</t>
   </si>
   <si>
     <t>callous </t>
   </si>
   <si>
     <t>heartless</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>麻木不仁的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强烈的，激烈的</t>
   </si>
   <si>
     <t>vehemently</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>emphatically</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强烈的，激烈的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>癖好</t>
   </si>
   <si>
     <t>predilection</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">proclivity </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>癖好</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔑视</t>
   </si>
   <si>
     <t>flouted</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蔑视</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>defied</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仓促的</t>
   </si>
   <si>
     <t>cursory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>fleeting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仓促的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>衰老</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>senescence</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>decrepitude</t>
   </si>
   <si>
     <t>似是而非的，欺骗的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>specious</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>fallacious</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equivocal</t>
+  </si>
+  <si>
+    <t>详细的</t>
   </si>
   <si>
     <t>meticulous</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>thorough</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>详细的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>笨拙的</t>
   </si>
   <si>
     <t>awkward</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ungainly</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>笨拙的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>榜样</t>
   </si>
   <si>
     <t>an exemplar for</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>榜样</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>a polestar of</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>异国的，不寻常的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>exotic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>anomalous</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普遍存在的</t>
   </si>
   <si>
     <t>omnipresent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ubiquitous</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普遍存在的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>过时的</t>
   </si>
   <si>
     <t>outmoded</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>unfashionable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>过时的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发誓放弃</t>
   </si>
   <si>
     <t>eschew</t>
@@ -280,109 +239,937 @@
     <t>forswear</t>
   </si>
   <si>
-    <t>发誓放弃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>forgo（放弃）</t>
+  </si>
+  <si>
+    <t>表露</t>
   </si>
   <si>
     <t>evince</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>betray</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表露</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缓和</t>
   </si>
   <si>
     <t>temper</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>neutralize</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缓和</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>萌芽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>seed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>germ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赞颂</t>
   </si>
   <si>
     <t>tributes to</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>encomiums to</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赞颂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laud</t>
+  </si>
+  <si>
+    <t>纯洁的</t>
   </si>
   <si>
     <t>unalloyed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>unadulterated </t>
   </si>
   <si>
-    <t>纯洁的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>多才多能不可或缺</t>
   </si>
   <si>
     <t>versatile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多才多能不可或缺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>indispensable</t>
+  </si>
+  <si>
+    <t>少量</t>
+  </si>
+  <si>
+    <t>paucity</t>
+  </si>
+  <si>
+    <t>modicum</t>
+  </si>
+  <si>
+    <t>dearth</t>
+  </si>
+  <si>
+    <t>paltry（无价值的）</t>
+  </si>
+  <si>
+    <t>乐观的</t>
+  </si>
+  <si>
+    <t>sanguine</t>
+  </si>
+  <si>
+    <t>optimistic</t>
+  </si>
+  <si>
+    <t>隐藏</t>
+  </si>
+  <si>
+    <t>conceal</t>
+  </si>
+  <si>
+    <t>belie （掩饰）</t>
+  </si>
+  <si>
+    <t>dissemblance（掩饰）</t>
+  </si>
+  <si>
+    <t>反复无常的</t>
+  </si>
+  <si>
+    <t>capricious</t>
+  </si>
+  <si>
+    <t>whimsical</t>
+  </si>
+  <si>
+    <t>讽</t>
+  </si>
+  <si>
+    <t>lampoon</t>
+  </si>
+  <si>
+    <t>corrosive</t>
+  </si>
+  <si>
+    <t>pastiche</t>
+  </si>
+  <si>
+    <t>mordant</t>
+  </si>
+  <si>
+    <t>奢华的</t>
+  </si>
+  <si>
+    <t>palatial</t>
+  </si>
+  <si>
+    <t>ornateness</t>
+  </si>
+  <si>
+    <t>sumptuous</t>
+  </si>
+  <si>
+    <t>lavish</t>
+  </si>
+  <si>
+    <t>grandiloquent</t>
+  </si>
+  <si>
+    <t>底层的，平民的</t>
+  </si>
+  <si>
+    <t>humble</t>
+  </si>
+  <si>
+    <t>pedestrian</t>
+  </si>
+  <si>
+    <t>声名狼藉的</t>
+  </si>
+  <si>
+    <t>disreputable</t>
+  </si>
+  <si>
+    <t>阻碍</t>
+  </si>
+  <si>
+    <t>encumber</t>
+  </si>
+  <si>
+    <t>impede</t>
+  </si>
+  <si>
+    <t>检查</t>
+  </si>
+  <si>
+    <t>scrutiny</t>
+  </si>
+  <si>
+    <t>inspection</t>
+  </si>
+  <si>
+    <t>避开</t>
+  </si>
+  <si>
+    <t>shun</t>
+  </si>
+  <si>
+    <t>忽视</t>
+  </si>
+  <si>
+    <t>ignore</t>
+  </si>
+  <si>
+    <t>oversee</t>
+  </si>
+  <si>
+    <t>disregard</t>
+  </si>
+  <si>
+    <t>承诺</t>
+  </si>
+  <si>
+    <t>undertaking</t>
+  </si>
+  <si>
+    <t>promise</t>
+  </si>
+  <si>
+    <t>说教的</t>
+  </si>
+  <si>
+    <t>sanctimonious</t>
+  </si>
+  <si>
+    <t>危险/动荡</t>
+  </si>
+  <si>
+    <t>perilous (危险)</t>
+  </si>
+  <si>
+    <t>upheaval</t>
+  </si>
+  <si>
+    <t>convulsion （抽搐，骚动）</t>
+  </si>
+  <si>
+    <t>可能出错的</t>
+  </si>
+  <si>
+    <t>fallible</t>
+  </si>
+  <si>
+    <t>erronesous</t>
+  </si>
+  <si>
+    <t>拥护</t>
+  </si>
+  <si>
+    <t>espouse</t>
+  </si>
+  <si>
+    <t>champion</t>
+  </si>
+  <si>
+    <t>严格</t>
+  </si>
+  <si>
+    <t>stringent</t>
+  </si>
+  <si>
+    <t>rigor</t>
+  </si>
+  <si>
+    <t>复兴</t>
+  </si>
+  <si>
+    <t>resurgence</t>
+  </si>
+  <si>
+    <t>Renaissance</t>
+  </si>
+  <si>
+    <t>revivify</t>
+  </si>
+  <si>
+    <t>削弱金钱</t>
+  </si>
+  <si>
+    <t>retrench（削弱开支）</t>
+  </si>
+  <si>
+    <t>undercut（削价竞争）</t>
+  </si>
+  <si>
+    <t>不偏不倚公正的</t>
+  </si>
+  <si>
+    <t>evenhanded</t>
+  </si>
+  <si>
+    <t>impartial</t>
+  </si>
+  <si>
+    <t>撒谎的，虚假的</t>
+  </si>
+  <si>
+    <t>mendacious</t>
+  </si>
+  <si>
+    <t>dissemblance</t>
+  </si>
+  <si>
+    <t>乏味的，陈词滥调</t>
+  </si>
+  <si>
+    <t>banality</t>
+  </si>
+  <si>
+    <t>bromide</t>
+  </si>
+  <si>
+    <t>好斗的</t>
+  </si>
+  <si>
+    <t>belligerence</t>
+  </si>
+  <si>
+    <t>aggressive</t>
+  </si>
+  <si>
+    <t>妥协</t>
+  </si>
+  <si>
+    <t>attune</t>
+  </si>
+  <si>
+    <t>compromise</t>
+  </si>
+  <si>
+    <t>坚定的，忠诚的</t>
+  </si>
+  <si>
+    <t>stalwart</t>
+  </si>
+  <si>
+    <t>坚不可摧的</t>
+  </si>
+  <si>
+    <t>impregnable</t>
+  </si>
+  <si>
+    <t>关心的，焦虑的</t>
+  </si>
+  <si>
+    <t>solicitous</t>
+  </si>
+  <si>
+    <t>起源</t>
+  </si>
+  <si>
+    <t>provenance</t>
+  </si>
+  <si>
+    <t>gensis</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>正直</t>
+  </si>
+  <si>
+    <t>rectitude</t>
+  </si>
+  <si>
+    <t>疏远</t>
+  </si>
+  <si>
+    <t>estrange</t>
+  </si>
+  <si>
+    <t>隔离</t>
+  </si>
+  <si>
+    <t>insulate</t>
+  </si>
+  <si>
+    <t>quarantine</t>
+  </si>
+  <si>
+    <t>sequester</t>
+  </si>
+  <si>
+    <t>shroud（视线中隔离）</t>
+  </si>
+  <si>
+    <t>segregation</t>
+  </si>
+  <si>
+    <t>cleave</t>
+  </si>
+  <si>
+    <t>紧贴</t>
+  </si>
+  <si>
+    <t>adhere</t>
+  </si>
+  <si>
+    <t>sting</t>
+  </si>
+  <si>
+    <t>任人唯亲</t>
+  </si>
+  <si>
+    <t>cronyism</t>
+  </si>
+  <si>
+    <t>nepotism</t>
+  </si>
+  <si>
+    <t>尖酸的，刻薄的</t>
+  </si>
+  <si>
+    <t>caustic</t>
+  </si>
+  <si>
+    <t>过剩的</t>
+  </si>
+  <si>
+    <t>exorbitance</t>
+  </si>
+  <si>
+    <t>superfluous</t>
+  </si>
+  <si>
+    <t>opulence</t>
+  </si>
+  <si>
+    <t>聪明的</t>
+  </si>
+  <si>
+    <t>resourcefulness</t>
+  </si>
+  <si>
+    <t>灵巧的</t>
+  </si>
+  <si>
+    <t>deftly</t>
+  </si>
+  <si>
+    <t>agile</t>
+  </si>
+  <si>
+    <t>刺</t>
+  </si>
+  <si>
+    <t>strident</t>
+  </si>
+  <si>
+    <t>spur</t>
+  </si>
+  <si>
+    <t>奇妙的</t>
+  </si>
+  <si>
+    <t>wondrous</t>
+  </si>
+  <si>
+    <t>心情好的/开心的</t>
+  </si>
+  <si>
+    <t>buoyancy （轻浮的）</t>
+  </si>
+  <si>
+    <t>blithe</t>
+  </si>
+  <si>
+    <t>诡辩者</t>
+  </si>
+  <si>
+    <t>quibbler</t>
+  </si>
+  <si>
+    <t>sophist</t>
+  </si>
+  <si>
+    <t>吹毛求疵的</t>
+  </si>
+  <si>
+    <t>cavil</t>
+  </si>
+  <si>
+    <t>告诫，警告</t>
+  </si>
+  <si>
+    <t>caveat</t>
+  </si>
+  <si>
+    <t>admonitory</t>
+  </si>
+  <si>
+    <t>安慰</t>
+  </si>
+  <si>
+    <t>soothe</t>
+  </si>
+  <si>
+    <t>placative</t>
+  </si>
+  <si>
+    <t>建议</t>
+  </si>
+  <si>
+    <t>pointer</t>
+  </si>
+  <si>
+    <t>admonishment</t>
+  </si>
+  <si>
+    <t>劝告</t>
+  </si>
+  <si>
+    <t>exhortation</t>
+  </si>
+  <si>
+    <t>dissuade</t>
+  </si>
+  <si>
+    <t>hortative</t>
+  </si>
+  <si>
+    <t>诱惑</t>
+  </si>
+  <si>
+    <t>allurement</t>
+  </si>
+  <si>
+    <t>temptation</t>
+  </si>
+  <si>
+    <t>任性的</t>
+  </si>
+  <si>
+    <t>obstreperous</t>
+  </si>
+  <si>
+    <t>dogged</t>
+  </si>
+  <si>
+    <t>dormant</t>
+  </si>
+  <si>
+    <t>浮夸的</t>
+  </si>
+  <si>
+    <t>bombastic</t>
+  </si>
+  <si>
+    <t>不明智的</t>
+  </si>
+  <si>
+    <t>imprudent</t>
+  </si>
+  <si>
+    <t>即兴的</t>
+  </si>
+  <si>
+    <t>extemporize</t>
+  </si>
+  <si>
+    <t>improvison</t>
+  </si>
+  <si>
+    <t>附属的，次要的</t>
+  </si>
+  <si>
+    <t>affiliated</t>
+  </si>
+  <si>
+    <t>ancillary</t>
+  </si>
+  <si>
+    <t>subsidiary</t>
+  </si>
+  <si>
+    <t>生气</t>
+  </si>
+  <si>
+    <t>sulk</t>
+  </si>
+  <si>
+    <t>tantrum</t>
+  </si>
+  <si>
+    <t>testy</t>
+  </si>
+  <si>
+    <t>indignant</t>
+  </si>
+  <si>
+    <t>apoplectic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -390,9 +1177,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -400,17 +1429,61 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -459,7 +1532,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -494,7 +1567,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -668,26 +1741,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G83"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" customWidth="1"/>
-    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="1" max="2" width="17.8333333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="21.8416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.425" customWidth="1"/>
+    <col min="6" max="6" width="16.925" customWidth="1"/>
+    <col min="7" max="7" width="19.4833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -698,305 +1769,973 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1" spans="1:3">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" t="s">
+        <v>113</v>
+      </c>
+      <c r="D35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>142</v>
+      </c>
+      <c r="B44" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" t="s">
+        <v>153</v>
+      </c>
+      <c r="D47" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>155</v>
+      </c>
+      <c r="B48" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>158</v>
+      </c>
+      <c r="B49" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" t="s">
+        <v>162</v>
+      </c>
+      <c r="C50" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>164</v>
+      </c>
+      <c r="B51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>173</v>
+      </c>
+      <c r="B54" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>175</v>
+      </c>
+      <c r="B55" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>177</v>
+      </c>
+      <c r="B56" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>179</v>
+      </c>
+      <c r="B57" t="s">
+        <v>180</v>
+      </c>
+      <c r="C57" t="s">
+        <v>181</v>
+      </c>
+      <c r="D57" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>183</v>
+      </c>
+      <c r="B58" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>185</v>
+      </c>
+      <c r="B59" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>187</v>
+      </c>
+      <c r="B60" t="s">
+        <v>188</v>
+      </c>
+      <c r="C60" t="s">
+        <v>189</v>
+      </c>
+      <c r="D60" t="s">
+        <v>190</v>
+      </c>
+      <c r="E60" t="s">
+        <v>191</v>
+      </c>
+      <c r="F60" t="s">
+        <v>192</v>
+      </c>
+      <c r="G60" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>194</v>
+      </c>
+      <c r="B61" t="s">
+        <v>195</v>
+      </c>
+      <c r="C61" t="s">
+        <v>196</v>
+      </c>
+      <c r="D61" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>197</v>
+      </c>
+      <c r="B62" t="s">
+        <v>198</v>
+      </c>
+      <c r="C62" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>202</v>
+      </c>
+      <c r="B64" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" t="s">
+        <v>204</v>
+      </c>
+      <c r="D64" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>206</v>
+      </c>
+      <c r="B65" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>208</v>
+      </c>
+      <c r="B66" t="s">
+        <v>209</v>
+      </c>
+      <c r="C66" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>211</v>
+      </c>
+      <c r="B67" t="s">
+        <v>212</v>
+      </c>
+      <c r="C67" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>214</v>
+      </c>
+      <c r="B68" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>216</v>
+      </c>
+      <c r="B69" t="s">
+        <v>217</v>
+      </c>
+      <c r="C69" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>219</v>
+      </c>
+      <c r="B70" t="s">
+        <v>220</v>
+      </c>
+      <c r="C70" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>222</v>
+      </c>
+      <c r="B71" t="s">
+        <v>220</v>
+      </c>
+      <c r="C71" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>224</v>
+      </c>
+      <c r="B72" t="s">
+        <v>225</v>
+      </c>
+      <c r="C72" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>227</v>
+      </c>
+      <c r="B73" t="s">
+        <v>228</v>
+      </c>
+      <c r="C73" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>230</v>
+      </c>
+      <c r="B74" t="s">
+        <v>231</v>
+      </c>
+      <c r="C74" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>233</v>
+      </c>
+      <c r="B75" t="s">
+        <v>234</v>
+      </c>
+      <c r="C75" t="s">
+        <v>235</v>
+      </c>
+      <c r="D75" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>237</v>
+      </c>
+      <c r="B76" t="s">
+        <v>238</v>
+      </c>
+      <c r="C76" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>240</v>
+      </c>
+      <c r="B77" t="s">
+        <v>241</v>
+      </c>
+      <c r="C77" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
+      <c r="B78" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>244</v>
+      </c>
+      <c r="B79" t="s">
+        <v>245</v>
+      </c>
+      <c r="C79" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B80" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>248</v>
+      </c>
+      <c r="B81" t="s">
+        <v>249</v>
+      </c>
+      <c r="C81" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>251</v>
+      </c>
+      <c r="B82" t="s">
+        <v>252</v>
+      </c>
+      <c r="C82" t="s">
+        <v>253</v>
+      </c>
+      <c r="D82" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>255</v>
+      </c>
+      <c r="B83" t="s">
+        <v>256</v>
+      </c>
+      <c r="C83" t="s">
+        <v>257</v>
+      </c>
+      <c r="D83" t="s">
+        <v>258</v>
+      </c>
+      <c r="E83" t="s">
+        <v>259</v>
+      </c>
+      <c r="F83" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/6 XUAN 2.xlsx
+++ b/6 XUAN 2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\69450\projects\3000\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB414B2-C7E3-4508-B4C2-67E81C393FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="10508" windowHeight="5502"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="344">
   <si>
     <t>谴责；指责，批评</t>
   </si>
@@ -596,233 +602,564 @@
     <t>insulate</t>
   </si>
   <si>
+    <t>sequester</t>
+  </si>
+  <si>
+    <t>shroud（视线中隔离）</t>
+  </si>
+  <si>
+    <t>segregation</t>
+  </si>
+  <si>
+    <t>cleave</t>
+  </si>
+  <si>
+    <t>紧贴</t>
+  </si>
+  <si>
+    <t>adhere</t>
+  </si>
+  <si>
+    <t>sting</t>
+  </si>
+  <si>
+    <t>任人唯亲</t>
+  </si>
+  <si>
+    <t>cronyism</t>
+  </si>
+  <si>
+    <t>nepotism</t>
+  </si>
+  <si>
+    <t>尖酸的，刻薄的</t>
+  </si>
+  <si>
+    <t>caustic</t>
+  </si>
+  <si>
+    <t>superfluous</t>
+  </si>
+  <si>
+    <t>opulence</t>
+  </si>
+  <si>
+    <t>聪明的</t>
+  </si>
+  <si>
+    <t>resourcefulness</t>
+  </si>
+  <si>
+    <t>灵巧的</t>
+  </si>
+  <si>
+    <t>deftly</t>
+  </si>
+  <si>
+    <t>agile</t>
+  </si>
+  <si>
+    <t>刺</t>
+  </si>
+  <si>
+    <t>strident</t>
+  </si>
+  <si>
+    <t>spur</t>
+  </si>
+  <si>
+    <t>奇妙的</t>
+  </si>
+  <si>
+    <t>wondrous</t>
+  </si>
+  <si>
+    <t>心情好的/开心的</t>
+  </si>
+  <si>
+    <t>buoyancy （轻浮的）</t>
+  </si>
+  <si>
+    <t>blithe</t>
+  </si>
+  <si>
+    <t>诡辩者</t>
+  </si>
+  <si>
+    <t>quibbler</t>
+  </si>
+  <si>
+    <t>sophist</t>
+  </si>
+  <si>
+    <t>吹毛求疵的</t>
+  </si>
+  <si>
+    <t>cavil</t>
+  </si>
+  <si>
+    <t>告诫，警告</t>
+  </si>
+  <si>
+    <t>caveat</t>
+  </si>
+  <si>
+    <t>admonitory</t>
+  </si>
+  <si>
+    <t>安慰</t>
+  </si>
+  <si>
+    <t>soothe</t>
+  </si>
+  <si>
+    <t>placative</t>
+  </si>
+  <si>
+    <t>建议</t>
+  </si>
+  <si>
+    <t>pointer</t>
+  </si>
+  <si>
+    <t>劝告</t>
+  </si>
+  <si>
+    <t>exhortation</t>
+  </si>
+  <si>
+    <t>dissuade</t>
+  </si>
+  <si>
+    <t>hortative</t>
+  </si>
+  <si>
+    <t>诱惑</t>
+  </si>
+  <si>
+    <t>allurement</t>
+  </si>
+  <si>
+    <t>temptation</t>
+  </si>
+  <si>
+    <t>任性的</t>
+  </si>
+  <si>
+    <t>obstreperous</t>
+  </si>
+  <si>
+    <t>dogged</t>
+  </si>
+  <si>
+    <t>dormant</t>
+  </si>
+  <si>
+    <t>浮夸的</t>
+  </si>
+  <si>
+    <t>bombastic</t>
+  </si>
+  <si>
+    <t>不明智的</t>
+  </si>
+  <si>
+    <t>imprudent</t>
+  </si>
+  <si>
+    <t>即兴的</t>
+  </si>
+  <si>
+    <t>extemporize</t>
+  </si>
+  <si>
+    <t>improvison</t>
+  </si>
+  <si>
+    <t>附属的，次要的</t>
+  </si>
+  <si>
+    <t>affiliated</t>
+  </si>
+  <si>
+    <t>ancillary</t>
+  </si>
+  <si>
+    <t>subsidiary</t>
+  </si>
+  <si>
+    <t>sulk</t>
+  </si>
+  <si>
+    <t>tantrum</t>
+  </si>
+  <si>
+    <t>testy</t>
+  </si>
+  <si>
+    <t>indignant</t>
+  </si>
+  <si>
+    <t>apoplectic</t>
+  </si>
+  <si>
+    <t>exhilarating （极其兴奋的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>恐惧</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>consternation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>appall</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚张声势</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bravodo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>swagger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>repudiate (否认)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pugnacious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>过剩的，大量的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>myraid（无限的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>turmoil</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>truculent</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游荡的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>peripatetic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>itinerant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>被。。。吸引</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dazzled by</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enthralling</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dampen（抑制）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>quarantine</t>
-  </si>
-  <si>
-    <t>sequester</t>
-  </si>
-  <si>
-    <t>shroud（视线中隔离）</t>
-  </si>
-  <si>
-    <t>segregation</t>
-  </si>
-  <si>
-    <t>cleave</t>
-  </si>
-  <si>
-    <t>紧贴</t>
-  </si>
-  <si>
-    <t>adhere</t>
-  </si>
-  <si>
-    <t>sting</t>
-  </si>
-  <si>
-    <t>任人唯亲</t>
-  </si>
-  <si>
-    <t>cronyism</t>
-  </si>
-  <si>
-    <t>nepotism</t>
-  </si>
-  <si>
-    <t>尖酸的，刻薄的</t>
-  </si>
-  <si>
-    <t>caustic</t>
-  </si>
-  <si>
-    <t>过剩的</t>
-  </si>
-  <si>
-    <t>exorbitance</t>
-  </si>
-  <si>
-    <t>superfluous</t>
-  </si>
-  <si>
-    <t>opulence</t>
-  </si>
-  <si>
-    <t>聪明的</t>
-  </si>
-  <si>
-    <t>resourcefulness</t>
-  </si>
-  <si>
-    <t>灵巧的</t>
-  </si>
-  <si>
-    <t>deftly</t>
-  </si>
-  <si>
-    <t>agile</t>
-  </si>
-  <si>
-    <t>刺</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>adamant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>固执的，无法动摇的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀薄</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dilute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>feign（制造假象）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>extol</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fractious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生气，愤怒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>困惑，迷惑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>befudd</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sententious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>节制的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>abstemious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unease</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不安，忧虑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>apprehension</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>diatribe（猛烈抨击）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>微不足道的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>paltry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>minute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ingenious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>evenhanded（公正）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mordancy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>分歧，争议</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>divergent</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dissension</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>contentious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>exorbitance(过高)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺耳的，喧闹的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>strident</t>
-  </si>
-  <si>
-    <t>spur</t>
-  </si>
-  <si>
-    <t>奇妙的</t>
-  </si>
-  <si>
-    <t>wondrous</t>
-  </si>
-  <si>
-    <t>心情好的/开心的</t>
-  </si>
-  <si>
-    <t>buoyancy （轻浮的）</t>
-  </si>
-  <si>
-    <t>blithe</t>
-  </si>
-  <si>
-    <t>诡辩者</t>
-  </si>
-  <si>
-    <t>quibbler</t>
-  </si>
-  <si>
-    <t>sophist</t>
-  </si>
-  <si>
-    <t>吹毛求疵的</t>
-  </si>
-  <si>
-    <t>cavil</t>
-  </si>
-  <si>
-    <t>告诫，警告</t>
-  </si>
-  <si>
-    <t>caveat</t>
-  </si>
-  <si>
-    <t>admonitory</t>
-  </si>
-  <si>
-    <t>安慰</t>
-  </si>
-  <si>
-    <t>soothe</t>
-  </si>
-  <si>
-    <t>placative</t>
-  </si>
-  <si>
-    <t>建议</t>
-  </si>
-  <si>
-    <t>pointer</t>
-  </si>
-  <si>
-    <t>admonishment</t>
-  </si>
-  <si>
-    <t>劝告</t>
-  </si>
-  <si>
-    <t>exhortation</t>
-  </si>
-  <si>
-    <t>dissuade</t>
-  </si>
-  <si>
-    <t>hortative</t>
-  </si>
-  <si>
-    <t>诱惑</t>
-  </si>
-  <si>
-    <t>allurement</t>
-  </si>
-  <si>
-    <t>temptation</t>
-  </si>
-  <si>
-    <t>任性的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unwise</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>admonishment（警告）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>炫耀</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>panache</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>obstreperous</t>
-  </si>
-  <si>
-    <t>dogged</t>
-  </si>
-  <si>
-    <t>dormant</t>
-  </si>
-  <si>
-    <t>浮夸的</t>
-  </si>
-  <si>
-    <t>bombastic</t>
-  </si>
-  <si>
-    <t>不明智的</t>
-  </si>
-  <si>
-    <t>imprudent</t>
-  </si>
-  <si>
-    <t>即兴的</t>
-  </si>
-  <si>
-    <t>extemporize</t>
-  </si>
-  <si>
-    <t>improvison</t>
-  </si>
-  <si>
-    <t>附属的，次要的</t>
-  </si>
-  <si>
-    <t>affiliated</t>
-  </si>
-  <si>
-    <t>ancillary</t>
-  </si>
-  <si>
-    <t>subsidiary</t>
-  </si>
-  <si>
-    <t>生气</t>
-  </si>
-  <si>
-    <t>sulk</t>
-  </si>
-  <si>
-    <t>tantrum</t>
-  </si>
-  <si>
-    <t>testy</t>
-  </si>
-  <si>
-    <t>indignant</t>
-  </si>
-  <si>
-    <t>apoplectic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>seethe（沸腾的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>resuscitate（复活）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>诽谤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspersions</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>slur</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pertinacity</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>steadfastness</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲动的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>madcap</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>aggressive</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>beguiling</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>阻碍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>inhibits</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>impedent</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>犹豫不决的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>vacillation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>lambaste</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>humdrum</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tedious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>monotone</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>单调的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>swung</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bemuse</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>indecision</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>acquainted</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>familiar</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>熟悉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>vociferous</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>deplore</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>deprecate （贬低）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>detract（贬低）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>besmirch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -831,151 +1168,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -984,192 +1200,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1177,313 +1213,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1741,58 +1498,73 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G83"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K102"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="17.8333333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="21.8416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.425" customWidth="1"/>
-    <col min="6" max="6" width="16.925" customWidth="1"/>
-    <col min="7" max="7" width="19.4833333333333" customWidth="1"/>
+    <col min="1" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.4140625" customWidth="1"/>
+    <col min="6" max="6" width="16.9140625" customWidth="1"/>
+    <col min="7" max="7" width="19.5" customWidth="1"/>
+    <col min="8" max="8" width="17.25" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
+    <col min="11" max="11" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="H1" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1803,7 +1575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1814,7 +1586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1825,7 +1597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1836,7 +1608,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1847,7 +1619,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1858,7 +1630,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1869,7 +1641,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1880,7 +1652,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1891,7 +1663,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1902,7 +1674,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1913,7 +1685,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1924,21 +1696,24 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
+    <row r="15" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="E15" s="8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -1949,7 +1724,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -1960,7 +1735,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" ht="13" customHeight="1" spans="1:3">
+    <row r="18" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -1971,7 +1746,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>58</v>
       </c>
@@ -1982,7 +1757,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -1993,7 +1768,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -2004,7 +1779,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -2018,7 +1793,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>71</v>
       </c>
@@ -2029,7 +1804,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -2040,7 +1815,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>77</v>
       </c>
@@ -2051,7 +1826,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -2064,8 +1839,11 @@
       <c r="D26" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="E26" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -2076,7 +1854,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -2087,7 +1865,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -2104,7 +1882,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>95</v>
       </c>
@@ -2115,7 +1893,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>98</v>
       </c>
@@ -2129,7 +1907,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>102</v>
       </c>
@@ -2140,24 +1918,33 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
+    <row r="33" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="F33" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>110</v>
       </c>
@@ -2177,7 +1964,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>116</v>
       </c>
@@ -2191,15 +1978,15 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
+    <row r="36" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>121</v>
       </c>
@@ -2209,8 +1996,11 @@
       <c r="C37" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>124</v>
       </c>
@@ -2221,7 +2011,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>127</v>
       </c>
@@ -2232,7 +2022,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>129</v>
       </c>
@@ -2246,7 +2036,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>133</v>
       </c>
@@ -2257,7 +2047,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>136</v>
       </c>
@@ -2267,22 +2057,28 @@
       <c r="C42" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
+      <c r="D42" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="8" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="E43" s="8" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>142</v>
       </c>
@@ -2293,7 +2089,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -2304,7 +2100,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -2315,7 +2111,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>151</v>
       </c>
@@ -2328,8 +2124,11 @@
       <c r="D47" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="E47" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>155</v>
       </c>
@@ -2340,7 +2139,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>158</v>
       </c>
@@ -2351,18 +2150,24 @@
         <v>160</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
+    <row r="50" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="8" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="D50" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>164</v>
       </c>
@@ -2373,7 +2178,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>167</v>
       </c>
@@ -2383,8 +2188,14 @@
       <c r="C52" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="D52" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>170</v>
       </c>
@@ -2395,23 +2206,26 @@
         <v>172</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
+    <row r="54" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="6" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
+      <c r="C54" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>177</v>
       </c>
@@ -2419,7 +2233,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>179</v>
       </c>
@@ -2433,309 +2247,548 @@
         <v>182</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>183</v>
       </c>
       <c r="B58" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
+      <c r="C58" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
-      <c r="A60" t="s">
+    <row r="60" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D60" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="G60" t="s">
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>194</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>195</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>196</v>
       </c>
-      <c r="D61" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>197</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>198</v>
       </c>
-      <c r="C62" t="s">
+    </row>
+    <row r="63" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="8" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
+      <c r="B63" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B63" t="s">
-        <v>109</v>
-      </c>
-      <c r="C63" t="s">
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C64" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
+      <c r="D64" t="s">
         <v>202</v>
       </c>
-      <c r="B64" t="s">
+      <c r="E64" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>203</v>
       </c>
-      <c r="C64" t="s">
+      <c r="B65" t="s">
         <v>204</v>
       </c>
-      <c r="D64" t="s">
+      <c r="C65" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
+      <c r="B66" t="s">
         <v>206</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C66" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>208</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>209</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
+    <row r="68" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C67" t="s">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
+      <c r="B69" t="s">
         <v>214</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C69" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
+      <c r="D69" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>216</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B70" t="s">
         <v>217</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>219</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B71" t="s">
+        <v>217</v>
+      </c>
+      <c r="C71" t="s">
         <v>220</v>
       </c>
-      <c r="C70" t="s">
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
+      <c r="B72" t="s">
         <v>222</v>
       </c>
-      <c r="B71" t="s">
-        <v>220</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="C72" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>224</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B73" t="s">
         <v>225</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C73" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>227</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>228</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C74" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
+      <c r="B75" t="s">
         <v>230</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C75" t="s">
         <v>231</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D75" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
-      <c r="A75" t="s">
+    <row r="76" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B76" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C76" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D75" t="s">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
+      <c r="B77" t="s">
         <v>237</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C77" t="s">
         <v>238</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D77" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>240</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B79" t="s">
         <v>241</v>
-      </c>
-      <c r="C77" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
-        <v>244</v>
-      </c>
-      <c r="B79" t="s">
-        <v>245</v>
       </c>
       <c r="C79" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>242</v>
+      </c>
+      <c r="B80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>244</v>
+      </c>
+      <c r="B81" t="s">
+        <v>245</v>
+      </c>
+      <c r="C81" t="s">
         <v>246</v>
       </c>
-      <c r="B80" t="s">
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
+      <c r="B82" t="s">
         <v>248</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C82" t="s">
         <v>249</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D82" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
+    <row r="83" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B83" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C83" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D83" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E83" s="8" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83" t="s">
+      <c r="F83" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="B83" t="s">
-        <v>256</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="G83" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D83" t="s">
+      <c r="B84" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="E83" t="s">
+      <c r="C84" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="F83" t="s">
+    </row>
+    <row r="85" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="8" t="s">
         <v>260</v>
       </c>
+      <c r="B85" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>337</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/6 XUAN 2.xlsx
+++ b/6 XUAN 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\69450\projects\3000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB414B2-C7E3-4508-B4C2-67E81C393FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646C64A1-FDB9-49C1-9016-AE89D56561AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,10 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="344">
-  <si>
-    <t>谴责；指责，批评</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="440">
   <si>
     <t>reprehended</t>
   </si>
@@ -1152,6 +1149,393 @@
   </si>
   <si>
     <t>besmirch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>obdurate （冷酷固执的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fractious（易怒的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ostentatious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>显然的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>conspicuous</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>prominent</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rambunctious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>captious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sparing</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pretentious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谄媚的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>obsequious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>obfuscate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>除去</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>obliterate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>obloquy（谩骂，诽谤）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>obstinate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>obstruct</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>obtuse（蠢）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>易腐的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>septic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>corrosive</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>florid（辞藻华丽的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉利的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>propitious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>auspicious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不吉利的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unpropitious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>portentous（夸张的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>prententious（做作的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>insentient</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>stupor</t>
+  </si>
+  <si>
+    <t>无感觉的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>presage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>prescient</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>预知</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mundane</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>circumscribe（限制）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>onerous</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cumbersome</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>繁重的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pervasive</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>渗透的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenuous （薄的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenuous（空洞的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可信的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>plausible</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>implausible</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可信的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>endorse（支持）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>divulge</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>泄露</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>formidable（榜样）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>艰难的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>formidable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>opprobrious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>parsimonious（过分节俭的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>particularize</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>complex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>meticulous</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>详尽的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrewd（狡猾的）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谴责；指责，批评，谩骂</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>recondite</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>深奥的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>减轻痛苦</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>salve</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>assuage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>excoriate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>opprobrium</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>迟钝的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sluggish</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>忍受</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>brook</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>endure</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>minuscule</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>minatory</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>venerable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>令人尊敬的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>brevity</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>succint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>简洁的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>glut（使过量）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>推测</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>surmise</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>友好的/和蔼的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>comity</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>affable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>争吵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>altercation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>blemish</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缺点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>损害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>glean</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>收集</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>flamboyance</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>attenuate</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1159,7 +1543,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1185,6 +1569,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1217,7 +1608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1229,6 +1620,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1504,1287 +1896,1650 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:N129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="25.25" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.83203125" customWidth="1"/>
-    <col min="5" max="5" width="19.4140625" customWidth="1"/>
+    <col min="4" max="5" width="21.83203125" customWidth="1"/>
     <col min="6" max="6" width="16.9140625" customWidth="1"/>
     <col min="7" max="7" width="19.5" customWidth="1"/>
     <col min="8" max="8" width="17.25" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
     <col min="11" max="11" width="11.75" customWidth="1"/>
+    <col min="12" max="12" width="24.25" customWidth="1"/>
+    <col min="14" max="14" width="12.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="B2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>43</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="B15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>49</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>52</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>58</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>59</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>61</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>62</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>64</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>65</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>67</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>68</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>69</v>
       </c>
-      <c r="D22" t="s">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>71</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>72</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>74</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>75</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>77</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>78</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>80</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>81</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>82</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>84</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>85</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>87</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>88</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>90</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>91</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>92</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>93</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>95</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>96</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>98</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>99</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>100</v>
       </c>
-      <c r="D31" t="s">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>102</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>103</v>
-      </c>
-      <c r="C32" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="C33" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="E33" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="F33" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G33" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H33" s="8" t="s">
         <v>341</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" t="s">
         <v>110</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>111</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>112</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>113</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>114</v>
       </c>
-      <c r="F34" t="s">
-        <v>115</v>
+      <c r="G34" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" t="s">
         <v>116</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" t="s">
         <v>117</v>
       </c>
-      <c r="C35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E35" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+      <c r="B36" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>120</v>
+      <c r="C36" s="5" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" t="s">
         <v>121</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>122</v>
       </c>
-      <c r="C37" t="s">
-        <v>123</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" t="s">
         <v>124</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>125</v>
-      </c>
-      <c r="C38" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" t="s">
         <v>127</v>
       </c>
-      <c r="B39" t="s">
-        <v>128</v>
-      </c>
       <c r="C39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" t="s">
         <v>129</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>130</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>131</v>
-      </c>
-      <c r="D40" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" t="s">
         <v>133</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>134</v>
-      </c>
-      <c r="C41" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" t="s">
         <v>136</v>
       </c>
-      <c r="B42" t="s">
-        <v>137</v>
-      </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="D43" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D43" s="8" t="s">
-        <v>141</v>
-      </c>
       <c r="E43" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" t="s">
         <v>142</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>143</v>
-      </c>
-      <c r="C44" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" t="s">
         <v>145</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>146</v>
       </c>
-      <c r="C45" t="s">
-        <v>147</v>
+      <c r="D45" s="2" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
         <v>148</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>149</v>
-      </c>
-      <c r="C46" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" t="s">
         <v>151</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>152</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>153</v>
       </c>
-      <c r="D47" t="s">
-        <v>154</v>
-      </c>
       <c r="E47" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>154</v>
+      </c>
+      <c r="B48" t="s">
         <v>155</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>156</v>
-      </c>
-      <c r="C48" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B49" t="s">
         <v>158</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>159</v>
-      </c>
-      <c r="C49" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="C50" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>163</v>
-      </c>
       <c r="D50" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" t="s">
         <v>164</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>165</v>
       </c>
-      <c r="C51" t="s">
-        <v>166</v>
+      <c r="D51" s="2" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" t="s">
         <v>167</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>168</v>
       </c>
-      <c r="C52" t="s">
-        <v>169</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>169</v>
+      </c>
+      <c r="B53" t="s">
         <v>170</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>171</v>
-      </c>
-      <c r="C53" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>174</v>
-      </c>
       <c r="C54" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>176</v>
+      </c>
+      <c r="B56" t="s">
         <v>177</v>
-      </c>
-      <c r="B56" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>178</v>
+      </c>
+      <c r="B57" t="s">
         <v>179</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>180</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>181</v>
-      </c>
-      <c r="D57" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>182</v>
+      </c>
+      <c r="B58" t="s">
         <v>183</v>
       </c>
-      <c r="B58" t="s">
-        <v>184</v>
-      </c>
       <c r="C58" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="C60" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D60" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="D60" s="8" t="s">
+      <c r="E60" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="F60" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="G60" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>192</v>
+      </c>
+      <c r="B61" t="s">
         <v>193</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>194</v>
       </c>
-      <c r="C61" t="s">
-        <v>195</v>
-      </c>
       <c r="D61" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>195</v>
+      </c>
+      <c r="B62" t="s">
         <v>196</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>197</v>
-      </c>
-      <c r="C62" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C64" t="s">
+        <v>200</v>
+      </c>
+      <c r="D64" t="s">
+        <v>201</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="F64" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>202</v>
+      </c>
+      <c r="B65" t="s">
+        <v>203</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>204</v>
+      </c>
+      <c r="B66" t="s">
+        <v>205</v>
+      </c>
+      <c r="C66" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>207</v>
+      </c>
+      <c r="B67" t="s">
+        <v>208</v>
+      </c>
+      <c r="C67" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>212</v>
+      </c>
+      <c r="B69" t="s">
+        <v>213</v>
+      </c>
+      <c r="C69" t="s">
+        <v>214</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>215</v>
+      </c>
+      <c r="B70" t="s">
+        <v>216</v>
+      </c>
+      <c r="C70" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>218</v>
+      </c>
+      <c r="B71" t="s">
+        <v>216</v>
+      </c>
+      <c r="C71" t="s">
+        <v>219</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>223</v>
+      </c>
+      <c r="B73" t="s">
+        <v>224</v>
+      </c>
+      <c r="C73" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>226</v>
+      </c>
+      <c r="B74" t="s">
+        <v>227</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>228</v>
+      </c>
+      <c r="B75" t="s">
+        <v>229</v>
+      </c>
+      <c r="C75" t="s">
+        <v>230</v>
+      </c>
+      <c r="D75" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>235</v>
+      </c>
+      <c r="B77" t="s">
+        <v>236</v>
+      </c>
+      <c r="C77" t="s">
+        <v>237</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>239</v>
+      </c>
+      <c r="B79" t="s">
+        <v>240</v>
+      </c>
+      <c r="C79" t="s">
+        <v>114</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>241</v>
+      </c>
+      <c r="B80" t="s">
+        <v>242</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>243</v>
+      </c>
+      <c r="B81" t="s">
+        <v>244</v>
+      </c>
+      <c r="C81" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>246</v>
+      </c>
+      <c r="B82" t="s">
+        <v>247</v>
+      </c>
+      <c r="C82" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C64" t="s">
-        <v>201</v>
-      </c>
-      <c r="D64" t="s">
-        <v>202</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>203</v>
-      </c>
-      <c r="B65" t="s">
-        <v>204</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>205</v>
-      </c>
-      <c r="B66" t="s">
-        <v>206</v>
-      </c>
-      <c r="C66" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>208</v>
-      </c>
-      <c r="B67" t="s">
-        <v>209</v>
-      </c>
-      <c r="C67" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>213</v>
-      </c>
-      <c r="B69" t="s">
-        <v>214</v>
-      </c>
-      <c r="C69" t="s">
-        <v>215</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>216</v>
-      </c>
-      <c r="B70" t="s">
-        <v>217</v>
-      </c>
-      <c r="C70" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>219</v>
-      </c>
-      <c r="B71" t="s">
-        <v>217</v>
-      </c>
-      <c r="C71" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>221</v>
-      </c>
-      <c r="B72" t="s">
-        <v>222</v>
-      </c>
-      <c r="C72" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>224</v>
-      </c>
-      <c r="B73" t="s">
-        <v>225</v>
-      </c>
-      <c r="C73" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>227</v>
-      </c>
-      <c r="B74" t="s">
-        <v>228</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="B95" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>229</v>
-      </c>
-      <c r="B75" t="s">
-        <v>230</v>
-      </c>
-      <c r="C75" t="s">
-        <v>231</v>
-      </c>
-      <c r="D75" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>236</v>
-      </c>
-      <c r="B77" t="s">
-        <v>237</v>
-      </c>
-      <c r="C77" t="s">
-        <v>238</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>240</v>
-      </c>
-      <c r="B79" t="s">
-        <v>241</v>
-      </c>
-      <c r="C79" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>242</v>
-      </c>
-      <c r="B80" t="s">
-        <v>243</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>244</v>
-      </c>
-      <c r="B81" t="s">
-        <v>245</v>
-      </c>
-      <c r="C81" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>247</v>
-      </c>
-      <c r="B82" t="s">
-        <v>248</v>
-      </c>
-      <c r="C82" t="s">
-        <v>249</v>
-      </c>
-      <c r="D82" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C90" s="5" t="s">
+      <c r="B96" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="91" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D100" s="2" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B102" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>337</v>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C109" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" s="9" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" s="4" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" s="4" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C120" s="3"/>
+    </row>
+    <row r="121" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>

--- a/6 XUAN 2.xlsx
+++ b/6 XUAN 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\69450\projects\3000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646C64A1-FDB9-49C1-9016-AE89D56561AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE80714-1044-419A-A00E-B68F32F05A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="501">
   <si>
     <t>reprehended</t>
   </si>
@@ -1536,6 +1536,250 @@
   </si>
   <si>
     <t>attenuate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有根据的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unjustified</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfounded</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfathomable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unintelligible</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法理解的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enigmatic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>secretive</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pristine</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>勤奋的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>assiduous</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>完美的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>impeccable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>animus</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rival</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌意的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>laborious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sedulous</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastidious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>immaculate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>consummate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>absolute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>garner</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>lethal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>noxious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>permeable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pernicious</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>persecute（折磨）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sabotage（迫害）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sabotage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>scourge（祸害）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>脆弱的</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>susceptible</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fragile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tamper（恶意篡改）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>foible（小缺点）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fracas</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>putative</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">speculate </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>stupor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>arcane</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>crabbed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>impugn（责难）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>knotty</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>揭露</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>debunk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>reveal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>exorcise</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>alienate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ironclad</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>agitate（煽動）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>esoteric</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>betray（流露）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>expostulate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>grate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>corroborate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>scrutiny</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sycophantic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ostensible</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1614,13 +1858,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1896,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.25" customWidth="1"/>
@@ -1910,64 +2156,68 @@
     <col min="11" max="11" width="11.75" customWidth="1"/>
     <col min="12" max="12" width="24.25" customWidth="1"/>
     <col min="14" max="14" width="12.4140625" customWidth="1"/>
+    <col min="15" max="15" width="14.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="O1" s="7" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1978,7 +2228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1989,7 +2239,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2000,7 +2250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -2011,7 +2261,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2022,7 +2272,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2033,7 +2283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2044,7 +2294,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2055,7 +2305,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -2066,7 +2316,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -2077,7 +2327,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -2088,7 +2338,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -2099,24 +2349,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F15" s="7" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -2259,6 +2512,9 @@
       <c r="C27" t="s">
         <v>85</v>
       </c>
+      <c r="D27" s="2" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -2327,29 +2583,29 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+    <row r="33" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="7" t="s">
         <v>341</v>
       </c>
     </row>
@@ -2396,14 +2652,14 @@
         <v>379</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>398</v>
       </c>
     </row>
@@ -2481,31 +2737,34 @@
       <c r="B42" t="s">
         <v>136</v>
       </c>
-      <c r="C42" t="s">
-        <v>124</v>
+      <c r="C42" s="2" t="s">
+        <v>498</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="43" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+    <row r="43" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="7" t="s">
         <v>349</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -2532,6 +2791,9 @@
       <c r="D45" s="2" t="s">
         <v>392</v>
       </c>
+      <c r="E45" s="2" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -2583,20 +2845,20 @@
         <v>159</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="s">
+    <row r="50" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="7" t="s">
         <v>321</v>
       </c>
     </row>
@@ -2642,23 +2904,26 @@
         <v>171</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
+    <row r="54" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="4" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
+    <row r="55" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="5" t="s">
         <v>175</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2694,34 +2959,37 @@
         <v>297</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
+    <row r="59" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="5" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="8" t="s">
+      <c r="C59" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="F60" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="G60" s="7" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2750,14 +3018,14 @@
         <v>197</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="8" t="s">
+    <row r="63" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="7" t="s">
         <v>199</v>
       </c>
     </row>
@@ -2817,11 +3085,11 @@
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
+    <row r="68" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="3" t="s">
         <v>211</v>
       </c>
     </row>
@@ -2864,14 +3132,14 @@
         <v>350</v>
       </c>
     </row>
-    <row r="72" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="8" t="s">
+    <row r="72" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="7" t="s">
         <v>222</v>
       </c>
     </row>
@@ -2911,14 +3179,14 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="8" t="s">
+    <row r="76" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="7" t="s">
         <v>234</v>
       </c>
     </row>
@@ -2936,11 +3204,11 @@
         <v>282</v>
       </c>
     </row>
-    <row r="78" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="4" t="s">
+    <row r="78" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="5" t="s">
         <v>238</v>
       </c>
     </row>
@@ -3000,54 +3268,54 @@
         <v>249</v>
       </c>
     </row>
-    <row r="83" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="8" t="s">
+    <row r="83" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="D83" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E83" s="8" t="s">
+      <c r="E83" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="F83" s="8" t="s">
+      <c r="F83" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="G83" s="8" t="s">
+      <c r="G83" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="H83" s="8" t="s">
+      <c r="H83" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="I83" s="8" t="s">
+      <c r="I83" s="7" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="84" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="8" t="s">
+    <row r="84" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="7" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="85" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="8" t="s">
+    <row r="85" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="7" t="s">
         <v>261</v>
       </c>
     </row>
@@ -3073,62 +3341,62 @@
         <v>273</v>
       </c>
     </row>
-    <row r="88" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
+    <row r="88" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="D88" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E88" s="4" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="89" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="s">
+    <row r="89" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D89" s="4" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="90" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
+    <row r="90" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="D90" s="4" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="91" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
+    <row r="91" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="D91" s="4" t="s">
         <v>399</v>
       </c>
     </row>
@@ -3167,66 +3435,72 @@
       <c r="D94" s="2" t="s">
         <v>302</v>
       </c>
+      <c r="E94" s="2" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="95" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="s">
+      <c r="A95" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="D95" s="5" t="s">
+      <c r="D95" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E95" s="6" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
+      <c r="F95" s="6" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C96" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="D96" s="5" t="s">
+      <c r="D96" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E96" s="4" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="97" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="7" t="s">
+    <row r="97" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="C97" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="D97" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="E97" s="6" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="98" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="7" t="s">
+    <row r="98" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C98" s="6" t="s">
         <v>320</v>
       </c>
     </row>
@@ -3240,6 +3514,9 @@
       <c r="C99" s="2" t="s">
         <v>324</v>
       </c>
+      <c r="D99" s="4" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
@@ -3291,30 +3568,36 @@
         <v>348</v>
       </c>
     </row>
-    <row r="104" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="8" t="s">
+    <row r="104" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="7" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
+      <c r="C104" s="7" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="4" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
+      <c r="C105" s="4" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="7" t="s">
         <v>364</v>
       </c>
     </row>
@@ -3329,18 +3612,21 @@
         <v>368</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
+    <row r="108" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D108" s="7" t="s">
         <v>419</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -3365,100 +3651,120 @@
         <v>377</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+    <row r="111" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="7" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
+    <row r="112" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="4" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
+      <c r="C112" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="114" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="3" t="s">
+    <row r="114" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="6" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="115" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
+    <row r="115" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="4" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
+      <c r="C115" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="6" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" s="9" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="9" t="s">
+      <c r="C116" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" s="8" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B117" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="C117" s="9" t="s">
+      <c r="C117" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="D117" s="9" t="s">
+      <c r="D117" s="8" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="118" spans="1:4" s="4" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
+    <row r="118" spans="1:5" s="5" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="4" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" s="6" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="5" t="s">
+      <c r="C118" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" s="5" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B119" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="C119" s="4" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="120" spans="1:4" s="4" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
+    <row r="120" spans="1:5" s="5" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C120" s="3"/>
-    </row>
-    <row r="121" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C120" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>415</v>
       </c>
@@ -3469,7 +3775,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>421</v>
       </c>
@@ -3480,7 +3786,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>424</v>
       </c>
@@ -3491,15 +3797,21 @@
         <v>423</v>
       </c>
     </row>
-    <row r="124" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
+    <row r="124" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="4" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C124" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>428</v>
       </c>
@@ -3510,36 +3822,172 @@
         <v>430</v>
       </c>
     </row>
-    <row r="126" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
+    <row r="126" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="6" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
+      <c r="C126" s="6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="6" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
+      <c r="C127" s="6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="6" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
+      <c r="C128" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="4" t="s">
         <v>436</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E132" s="4"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
